--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,148 +466,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,106 +617,106 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -726,44 +726,44 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -773,44 +773,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -820,44 +820,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -867,44 +867,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,44 +914,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -971,34 +971,34 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1030,22 +1030,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1060,91 +1060,91 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>1.511</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.593</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.5511</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1.5958</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1.5997</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1154,44 +1154,44 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1201,44 +1201,44 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1248,86 +1248,86 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,91 +1337,91 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,472 +1431,472 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1911,39 +1911,39 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1958,39 +1958,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2017,27 +2017,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2064,27 +2064,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2111,32 +2111,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2146,101 +2146,101 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,89 +2252,89 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2346,37 +2346,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2386,90 +2386,184 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,153 +466,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,148 +622,148 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -773,44 +773,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -820,44 +820,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -867,44 +867,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,44 +914,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,44 +961,44 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1018,34 +1018,34 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1077,22 +1077,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1124,22 +1124,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,49 +1149,49 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1201,44 +1201,44 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1248,44 +1248,44 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1295,39 +1295,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1342,96 +1342,96 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1441,34 +1441,34 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,44 +1478,44 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,227 +1525,227 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1755,101 +1755,101 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1859,91 +1859,91 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1958,39 +1958,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,27 +2017,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2052,39 +2052,39 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2099,39 +2099,39 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2146,39 +2146,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2193,44 +2193,44 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2240,86 +2240,86 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2329,49 +2329,49 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2381,49 +2381,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2433,34 +2433,34 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2487,74 +2487,106 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -2565,6 +2597,21 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,175 +491,175 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,148 +669,148 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -820,44 +820,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -867,44 +867,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,44 +914,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,44 +961,44 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,44 +1008,44 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1065,34 +1065,34 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1124,22 +1124,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1171,22 +1171,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,49 +1196,49 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1248,44 +1248,44 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1295,44 +1295,44 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1342,39 +1342,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1389,96 +1389,96 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1488,34 +1488,34 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,44 +1525,44 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,227 +1572,227 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1802,101 +1802,101 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1906,91 +1906,91 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2064,27 +2064,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2099,39 +2099,39 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2146,39 +2146,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2193,39 +2193,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2240,44 +2240,44 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2287,86 +2287,86 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2376,49 +2376,49 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2428,49 +2428,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2480,34 +2480,34 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2534,74 +2534,106 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2612,6 +2644,21 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,69 +466,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,175 +538,175 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,148 +716,148 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -867,44 +867,44 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,44 +914,44 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,44 +961,44 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,44 +1008,44 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,44 +1055,44 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1112,34 +1112,34 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1171,22 +1171,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1218,22 +1218,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,49 +1243,49 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1295,44 +1295,44 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1342,44 +1342,44 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1389,39 +1389,39 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1436,96 +1436,96 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1535,34 +1535,34 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,44 +1572,44 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1619,227 +1619,227 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1849,101 +1849,101 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1953,91 +1953,91 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2052,39 +2052,39 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2111,27 +2111,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2146,39 +2146,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2193,39 +2193,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2240,39 +2240,39 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2287,44 +2287,44 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2334,86 +2334,86 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2423,49 +2423,49 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2475,49 +2475,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2527,34 +2527,34 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2581,74 +2581,106 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -2659,6 +2691,21 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,383 +466,383 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>1.558</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>1.567</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,106 +852,106 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,44 +961,44 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,44 +1008,44 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,44 +1055,44 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,44 +1102,44 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,44 +1149,44 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1206,34 +1206,34 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,22 +1265,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1295,91 +1295,91 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>1.511</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.593</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1.5511</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.5958</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1.5997</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1389,44 +1389,44 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1483,86 +1483,86 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,91 +1572,91 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1666,472 +1666,472 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2146,39 +2146,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2193,39 +2193,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2252,27 +2252,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2299,27 +2299,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2346,32 +2346,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2381,101 +2381,101 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2487,89 +2487,89 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,37 +2581,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2621,90 +2621,184 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,111 +466,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -580,96 +580,96 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -679,175 +679,175 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -857,148 +857,148 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,44 +1008,44 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1055,44 +1055,44 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,44 +1102,44 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,44 +1149,44 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,44 +1196,44 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1253,34 +1253,34 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1312,22 +1312,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1359,22 +1359,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,49 +1384,49 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1483,44 +1483,44 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1530,39 +1530,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1577,96 +1577,96 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1713,44 +1713,44 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1760,227 +1760,227 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1990,101 +1990,101 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2094,91 +2094,91 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2193,39 +2193,39 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2252,27 +2252,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2287,39 +2287,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2334,39 +2334,39 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2381,39 +2381,39 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2428,44 +2428,44 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2475,86 +2475,86 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2564,49 +2564,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2616,49 +2616,49 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2668,34 +2668,34 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2722,74 +2722,106 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -2800,6 +2832,21 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,54 +466,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,623 +523,623 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>1.547</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.558</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1.528</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>1.538</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.5516</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>1.543</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>1.556</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.567</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1149,44 +1149,44 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>1.586</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1.595</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1196,44 +1196,44 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1243,44 +1243,44 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,44 +1290,44 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,44 +1337,44 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,44 +1384,44 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,123 +1446,123 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1.5511</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.5958</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.5997</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1577,44 +1577,44 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1624,86 +1624,86 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1713,44 +1713,44 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1760,514 +1760,514 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>1.609</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1.617</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2277,49 +2277,49 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2334,19 +2334,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2393,27 +2393,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2428,39 +2428,39 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2475,44 +2475,44 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2522,81 +2522,81 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2606,59 +2606,59 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2668,39 +2668,39 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2710,54 +2710,54 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2769,42 +2769,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2816,36 +2816,177 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,54 +466,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,138 +523,138 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>1.527</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>1.538</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.5515</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,623 +664,623 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>1.547</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.558</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>1.528</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1.538</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.5516</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>1.543</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>1.556</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.567</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,44 +1290,44 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>1.586</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1.595</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,44 +1337,44 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,44 +1384,44 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,44 +1431,44 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,44 +1478,44 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,44 +1525,44 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1587,123 +1587,123 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1.5511</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.5958</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.5997</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1765,86 +1765,86 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1854,44 +1854,44 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,514 +1901,514 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>1.609</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>1.617</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2418,49 +2418,49 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2475,19 +2475,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2534,27 +2534,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2569,39 +2569,39 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2616,44 +2616,44 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2663,81 +2663,81 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2747,59 +2747,59 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2809,39 +2809,39 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2851,54 +2851,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2910,42 +2910,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2957,36 +2957,177 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,440 +466,440 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1.4985</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.5135</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.5242</t>
+          <t>1.5205</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5342</t>
+          <t>1.5315</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5441</t>
+          <t>1.5405</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5155</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5265</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5455</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -909,96 +909,96 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,175 +1008,175 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1186,148 +1186,148 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,44 +1337,44 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1384,44 +1384,44 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1431,44 +1431,44 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1478,44 +1478,44 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,44 +1525,44 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1582,34 +1582,34 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1641,22 +1641,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1688,22 +1688,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1713,49 +1713,49 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1765,44 +1765,44 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1812,44 +1812,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1859,39 +1859,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1906,96 +1906,96 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2005,34 +2005,34 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2042,44 +2042,44 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2089,227 +2089,227 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2319,101 +2319,101 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6269</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.639</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2423,91 +2423,91 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2522,39 +2522,39 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2581,27 +2581,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2616,39 +2616,39 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2663,39 +2663,39 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2710,39 +2710,39 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2757,44 +2757,44 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2804,86 +2804,86 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>12 Jan 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Jan 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.487</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2893,49 +2893,49 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.646</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>08 Jan 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.482</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2945,49 +2945,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.636</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>07 Jan 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.619</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2997,34 +2997,34 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>06 Jan 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.263</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3051,74 +3051,106 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>05 Jan 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.264</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.574</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.637</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3129,6 +3161,21 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>www.chinamoney.com.cn/english/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,2715 +466,4501 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1.407</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.392</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.5205</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.5315</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.5405</t>
+          <t>1.4675</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.372</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.5135</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.5242</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.5342</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.5441</t>
+          <t>1.4685</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.5155</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5265</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.5455</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.339</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.344</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.4305</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.466</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.467</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4335</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.4355</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.299</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.394</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.395</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1.414</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.441</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>1.457</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.495</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1.533</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1.542</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1.556</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.567</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.243</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.4745</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.242</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.364</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.424</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.446</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.4345</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.4695</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.4825</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.4745</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.4865</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.4645</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.4935</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.4665</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.4955</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.326</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4965</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.336</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4815</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4515</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4835</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.497</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.359</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.4765</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.4985</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4715</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.505</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.363</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.476</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.4895</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.5105</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4685</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.4945</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.5165</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.472</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.484</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.518</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.526</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4885</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.5145</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.5245</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.5345</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.536</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.4985</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.5205</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.5315</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.5405</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>1.5248</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.5358</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1.547</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>1.558</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.533</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.542</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.556</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>1.567</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>02 Mar 2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.315</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.466</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.514</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.5678</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.582</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1.5994</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1.318</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1.5679</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.5846</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1.5945</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1.604</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>27 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1.358</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.474</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.527</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.586</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1.605</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>26 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.368</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.529</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1.5748</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1.588</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1.5968</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1.6068</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>25 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.378</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1.497</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.571</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.5778</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1.5979</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1.608</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>24 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.362</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1.553</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.578</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.3156</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1.3233</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.271</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.511</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.593</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1.368</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.583</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.5951</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1.6089</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1.366</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.523</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.5511</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.5958</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.5997</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1.6092</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1.362</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.531</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1.604</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.551</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.5977</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1.602</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1.6115</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>09 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1.584</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.5967</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.6046</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1.6147</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>06 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1.277</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1.504</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1.6058</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1.6169</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>05 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1.319</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.464</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1.614</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.5505</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.5805</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.6079</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1.6189</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>04 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.318</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1.473</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1.583</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1.5846</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1.609</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>03 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.317</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1.488</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1.511</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.5859</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.6042</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1.6104</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1.6215</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>02 Feb 2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.365</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.509</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1.5889</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1.6069</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.6137</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1.6248</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1.328</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.551</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1.589</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.609</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1.628</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>29 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.368</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1.572</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.552</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.608</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1.629</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>28 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.366</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.527</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.5546</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1.5947</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.6099</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1.6189</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1.6337</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>27 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.371</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.5556</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1.5968</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.6094</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1.543</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5558</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.5978</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1.6135</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1.6269</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.396</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1.491</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.5577</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1.629</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1.6441</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1.413</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1.497</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.616</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.6327</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1.6458</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.322</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1.488</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1.483</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.582</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1.638</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1.318</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1.467</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.501</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.496</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.558</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.5596</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.567</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.391</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1.523</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1.316</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1.473</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.489</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.556</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.272</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1.461</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1.487</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1.635</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1.646</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1.462</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.482</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1.636</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.266</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1.453</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,178 +466,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.465</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.4045</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -647,1048 +647,1048 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.463</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.4305</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.4325</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.354</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.3885</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.4335</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.3865</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.4355</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.459</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1.348</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.427</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.459</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>1.347</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4605</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4625</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.379</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4645</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>1.362</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>1.381</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.383</t>
-        </is>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.4055</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.377</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.402</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>1.391</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1.396</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.4665</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1.407</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.392</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.4675</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.372</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.4685</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4015</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>1.4065</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>1.429</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.446</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.339</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.344</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.4345</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.4535</t>
+          <t>1.4305</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.4695</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.466</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.4375</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.4865</t>
+          <t>1.467</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.4645</t>
+          <t>1.4335</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.4935</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.4355</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1.299</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.4965</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.394</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>1.438</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>1.469</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.4815</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1698,2174 +1698,2174 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4515</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.4835</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4535</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.4635</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.4715</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.4895</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.5105</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.4945</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.5165</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.243</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.4745</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.242</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.364</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.424</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4885</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.5145</t>
+          <t>1.446</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.5245</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.5345</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1.4345</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.4695</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4825</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4745</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4865</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.5205</t>
+          <t>1.4645</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.5315</t>
+          <t>1.478</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.5405</t>
+          <t>1.4935</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.5135</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.5242</t>
+          <t>1.4665</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.5342</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.5441</t>
+          <t>1.4955</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.326</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.5155</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.5265</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.5455</t>
+          <t>1.4965</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.336</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4815</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.4515</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4835</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.497</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.359</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4765</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.4985</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.4715</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.505</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.363</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.476</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4895</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.5105</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.4685</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.4945</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.5165</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.472</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.484</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.518</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.526</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.4885</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.5145</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.5245</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5345</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.536</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.4985</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5205</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5315</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5405</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>1.547</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.561</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.572</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>1.58</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>1.5958</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1.5997</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3875,44 +3875,44 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3922,1045 +3922,1797 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.578</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>1.599</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1.5558</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1.5978</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>1.6135</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1.6269</t>
-        </is>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.593</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>1.5805</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>1.5846</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>1.637</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1.648</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
+          <t>1.6269</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
           <t>1.639</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.396</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1.491</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.5577</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1.629</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1.6441</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1.413</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1.497</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1.616</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1.6327</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1.6458</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.322</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1.488</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1.483</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.582</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1.638</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.318</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1.467</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>1.501</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1.496</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.558</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.5596</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1.567</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1.391</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1.523</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.316</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1.473</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1.489</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.556</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1.272</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1.461</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1.487</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1.635</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1.646</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1.462</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1.482</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1.636</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.266</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.453</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,554 +466,554 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.513</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.517</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.4395</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.471</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.481</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.484</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.431</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.452</t>
+          <t>1.471</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1.482</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.499</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.462</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.489</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.402</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.391</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.354</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3885</t>
+          <t>1.4185</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.468</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4785</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3865</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.4015</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.4035</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.4605</t>
+          <t>1.465</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.4035</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.463</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1023,44 +1023,44 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.4645</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1070,269 +1070,269 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.354</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.3885</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.4055</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.3865</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.4045</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.459</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1.348</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.427</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.459</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.347</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.4605</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.4625</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1.379</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1342,59 +1342,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.4645</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.4045</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.452</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1406,252 +1406,252 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.4055</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.4305</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.4325</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.4335</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.4665</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.407</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.392</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.4355</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.4675</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.372</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.4685</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1661,2055 +1661,2055 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.339</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.344</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.4305</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.466</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.467</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.4335</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.4355</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>1.299</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.338</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>1.391</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1.396</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.394</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4015</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.446</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.4345</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.4535</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.4695</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.4375</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.4865</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.4645</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.4935</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.243</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.4745</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.242</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1.364</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.424</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.4965</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.446</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.4815</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4515</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.4835</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>1.412</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.4345</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>1.4535</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.4635</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>1.473</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4695</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.4825</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.4745</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.4865</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.4715</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.4645</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.478</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.4935</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.4895</t>
+          <t>1.4665</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.5105</t>
+          <t>1.4955</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1.326</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.4945</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.5165</t>
+          <t>1.4965</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.336</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.4815</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1.4515</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.4835</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4885</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.5145</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.5245</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.5345</t>
+          <t>1.497</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.359</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.4765</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1.4985</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1.4715</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.505</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.363</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.476</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4895</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5105</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.4685</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.5205</t>
+          <t>1.4945</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.5315</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1.5405</t>
+          <t>1.5165</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>1.369</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.472</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.484</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.496</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>1.506</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1.503</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.5135</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.5242</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1.5342</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.5441</t>
+          <t>1.518</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.5155</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.5265</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.5455</t>
+          <t>1.526</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4885</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.5145</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.5245</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.5345</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.536</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4985</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.5205</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.5315</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.5405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>1.522</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>1.547</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>1.561</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>1.572</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3719,232 +3719,232 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3954,247 +3954,247 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4204,44 +4204,44 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4251,44 +4251,44 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4298,138 +4298,138 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4439,44 +4439,44 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4486,91 +4486,91 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1.6079</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4580,44 +4580,44 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>1.593</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1.609</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4627,759 +4627,759 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>1.531</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1.604</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.551</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1.598</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>1.551</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1.589</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>29 Jan 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.552</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.608</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.618</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.629</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>28 Jan 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.596</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.5546</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5947</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6099</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6189</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6337</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>27 Jan 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.564</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.5556</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.624</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.637</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>26 Jan 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5978</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6135</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
+          <t>1.6269</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>1.639</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>23 Jan 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.491</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5577</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.629</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6441</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>22 Jan 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.616</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.6327</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6458</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5401,272 +5401,272 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>20 Jan 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.638</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>19 Jan 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.557</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>16 Jan 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5596</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.639</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>14 Jan 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>13 Jan 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.559</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5683,36 +5683,365 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1.316</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1.473</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1.489</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.556</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1.272</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1.461</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1.487</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1.635</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1.646</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1.462</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1.482</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1.636</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1.266</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1.453</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/data/excel/Shibor_Historical_Data_2026.xlsx
+++ b/backend/data/excel/Shibor_Historical_Data_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,32 +466,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26 Jun 2026</t>
+          <t>24 Jul 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.3812</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -501,180 +501,180 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.4691</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4791</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25 Jun 2026</t>
+          <t>23 Jul 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.513</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1.4395</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 Jun 2026</t>
+          <t>22 Jul 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.436</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.4755</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 Jun 2026</t>
+          <t>21 Jul 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.431</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.474</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22 Jun 2026</t>
+          <t>20 Jul 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.499</t>
+          <t>1.4345</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,44 +684,44 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4491</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4642</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4722</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18 Jun 2026</t>
+          <t>17 Jul 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.3971</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4199</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -731,1862 +731,1862 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4459</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4622</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.4722</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17 Jun 2026</t>
+          <t>16 Jul 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4185</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.4785</t>
+          <t>1.4715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16 Jun 2026</t>
+          <t>15 Jul 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.3925</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.4235</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.4168</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.463</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.4723</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15 Jun 2026</t>
+          <t>14 Jul 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1.4132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.4299</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1.4444</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.4624</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.4734</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12 Jun 2026</t>
+          <t>13 Jul 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.372</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4435</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.4735</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 Jun 2026</t>
+          <t>10 Jul 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.3601</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.4109</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.4279</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.431</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.452</t>
+          <t>1.4639</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1.4728</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10 Jun 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1.4135</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.4445</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4725</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09 Jun 2026</t>
+          <t>08 Jul 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.384</t>
+          <t>1.3663</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.3773</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.4151</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.4312</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4639</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4739</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08 Jun 2026</t>
+          <t>07 Jul 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.354</t>
+          <t>1.374</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3885</t>
+          <t>1.4158</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.4319</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.4453</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.4641</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4742</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05 Jun 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3865</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.4345</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.4775</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>03 Jul 2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.4015</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.427</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03 Jun 2026</t>
+          <t>02 Jul 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1.437</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1.426</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.4035</t>
+          <t>1.437</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.4605</t>
+          <t>1.479</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.463</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.426</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.4035</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01 Jun 2026</t>
+          <t>30 Jun 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.426</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.4645</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>29 Jun 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.356</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.427</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.4075</t>
+          <t>1.437</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28 May 2026</t>
+          <t>26 Jun 2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.389</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.4055</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>25 Jun 2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.513</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.517</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.4045</t>
+          <t>1.4395</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.471</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.481</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>24 Jun 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.402</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.484</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>23 Jun 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.471</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.482</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22 May 2026</t>
+          <t>22 Jun 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1.499</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21 May 2026</t>
+          <t>18 Jun 2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1.4065</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>17 Jun 2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.286</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3855</t>
+          <t>1.4185</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.4045</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.452</t>
+          <t>1.468</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.4785</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>16 Jun 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.4305</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>15 Jun 2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.4325</t>
+          <t>1.443</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.4545</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15 May 2026</t>
+          <t>12 Jun 2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1.453</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1.403</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.4335</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.465</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>11 Jun 2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.4355</t>
+          <t>1.431</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.4555</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.463</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>10 Jun 2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1.413</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.393</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.436</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.456</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>09 Jun 2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.384</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11 May 2026</t>
+          <t>08 Jun 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.354</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.3885</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09 May 2026</t>
+          <t>05 Jun 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.3865</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08 May 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.348</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>1.427</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>1.447</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1.459</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1.316</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.347</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>1.448</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.4605</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06 May 2026</t>
+          <t>02 Jun 2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>1.367</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>1.389</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4035</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1.4625</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30 Apr 2026</t>
+          <t>01 Jun 2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>1.379</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1.396</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.4645</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29 Apr 2026</t>
+          <t>29 May 2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1.387</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.4075</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>28 May 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1.4055</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.4465</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27 Apr 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4015</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>1.4045</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>1.429</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1.446</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.377</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.402</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.4505</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.4665</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.329</t>
+          <t>1.401</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.407</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.392</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.4345</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.4535</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.4695</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.4675</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22 Apr 2026</t>
+          <t>22 May 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.372</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4195</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.4375</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.4745</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.4865</t>
+          <t>1.4685</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21 Apr 2026</t>
+          <t>21 May 2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.288</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2596,556 +2596,556 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4265</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1.4065</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.4645</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.4935</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20 Apr 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.286</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.339</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1.344</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.3855</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1.4045</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.4665</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.452</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.4955</t>
+          <t>1.4655</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.334</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1.4525</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.4655</t>
+          <t>1.4305</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.4965</t>
+          <t>1.466</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.336</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.386</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.4325</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.4815</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.467</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>15 May 2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.313</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4515</t>
+          <t>1.388</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.408</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.4335</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.4835</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.4975</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.265</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4535</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.4635</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.4355</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4555</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1.299</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.409</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.4765</t>
+          <t>1.436</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.456</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.468</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.308</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.343</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4615</t>
+          <t>1.394</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.4715</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>11 May 2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1.4895</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.5105</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>09 May 2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4685</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.414</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.4945</t>
+          <t>1.444</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.458</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1.5165</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07 Apr 2026</t>
+          <t>08 May 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1.371</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1.398</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.447</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.469</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03 Apr 2026</t>
+          <t>07 May 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1.275</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1.381</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.383</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.479</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02 Apr 2026</t>
+          <t>06 May 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3155,1736 +3155,1736 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.389</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4885</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1.4995</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1.5145</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1.5245</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.5345</t>
+          <t>1.471</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01 Apr 2026</t>
+          <t>30 Apr 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.416</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1.472</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31 Mar 2026</t>
+          <t>29 Apr 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.243</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1.376</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4745</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30 Mar 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.242</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>1.364</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.382</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.399</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.424</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4465</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27 Mar 2026</t>
+          <t>27 Apr 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4985</t>
+          <t>1.4015</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.429</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1.5205</t>
+          <t>1.446</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.5315</t>
+          <t>1.459</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.5405</t>
+          <t>1.4765</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26 Mar 2026</t>
+          <t>24 Apr 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.503</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1.5135</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1.5242</t>
+          <t>1.4505</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.5342</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.5441</t>
+          <t>1.478</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25 Mar 2026</t>
+          <t>23 Apr 2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.329</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.5112</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5045</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1.5155</t>
+          <t>1.4345</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1.5265</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.4695</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.5455</t>
+          <t>1.4825</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>24 Mar 2026</t>
+          <t>22 Apr 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.219</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.4195</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1.516</t>
+          <t>1.4375</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4745</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4865</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23 Mar 2026</t>
+          <t>21 Apr 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.331</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5095</t>
+          <t>1.4265</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1.5182</t>
+          <t>1.442</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.4645</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.478</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.5485</t>
+          <t>1.4935</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20 Mar 2026</t>
+          <t>20 Apr 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.357</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1.449</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.4665</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.4955</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>19 Mar 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.326</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1.4525</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4655</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.481</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.5595</t>
+          <t>1.4965</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18 Mar 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.425</t>
+          <t>1.336</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.4815</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17 Mar 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.221</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1.4291</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.4795</t>
+          <t>1.373</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5248</t>
+          <t>1.4515</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.5358</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.4835</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.4975</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16 Mar 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1.441</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5283</t>
+          <t>1.4535</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1.4635</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1.5516</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1.5627</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.5716</t>
+          <t>1.497</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13 Mar 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1.224</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.359</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1.455</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1.542</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.4765</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1.576</t>
+          <t>1.4985</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12 Mar 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.353</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.4615</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1.4715</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.483</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.505</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11 Mar 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1.223</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.363</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>1.476</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1.561</t>
+          <t>1.4895</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5105</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10 Mar 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5359</t>
+          <t>1.4685</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1.5492</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1.5614</t>
+          <t>1.4945</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.5715</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1.5803</t>
+          <t>1.5165</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09 Mar 2026</t>
+          <t>07 Apr 2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.226</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.324</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1.369</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5392</t>
+          <t>1.472</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1.5515</t>
+          <t>1.484</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1.5636</t>
+          <t>1.496</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1.5746</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1.5825</t>
+          <t>1.518</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06 Mar 2026</t>
+          <t>03 Apr 2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.238</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.338</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.396</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.5417</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1.5548</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1.5759</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1.5848</t>
+          <t>1.526</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05 Mar 2026</t>
+          <t>02 Apr 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.404</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5468</t>
+          <t>1.4885</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.4995</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.5145</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.5245</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5345</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>04 Mar 2026</t>
+          <t>01 Apr 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1.421</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1.493</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1.5605</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1.5727</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.5826</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1.5915</t>
+          <t>1.536</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>03 Mar 2026</t>
+          <t>31 Mar 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1.469</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1.507</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.538</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>02 Mar 2026</t>
+          <t>30 Mar 2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1.418</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.514</t>
+          <t>1.494</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.5678</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1.5994</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28 Feb 2026</t>
+          <t>27 Mar 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.502</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.4985</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1.5679</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5205</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.5945</t>
+          <t>1.5315</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.5405</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27 Feb 2026</t>
+          <t>26 Mar 2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.358</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1.438</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.506</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.503</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.5135</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>1.5242</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5342</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.5441</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26 Feb 2026</t>
+          <t>25 Mar 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1.5112</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5045</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.5748</t>
+          <t>1.5155</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1.6068</t>
+          <t>1.5455</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25 Feb 2026</t>
+          <t>24 Mar 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1.571</t>
+          <t>1.512</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1.5778</t>
+          <t>1.516</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1.5979</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.547</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>24 Feb 2026</t>
+          <t>23 Mar 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1.553</t>
+          <t>1.422</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.524</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5095</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1.5182</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5485</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14 Feb 2026</t>
+          <t>20 Mar 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.3156</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.3233</t>
+          <t>1.417</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.522</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.534</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.555</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13 Feb 2026</t>
+          <t>19 Mar 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.489</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.528</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.5595</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>12 Feb 2026</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.425</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.532</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1.5951</t>
+          <t>1.543</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1.6089</t>
+          <t>1.565</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11 Feb 2026</t>
+          <t>17 Mar 2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.4291</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4795</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.5511</t>
+          <t>1.5248</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5358</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1.5958</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.5997</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1.6092</t>
+          <t>1.567</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10 Feb 2026</t>
+          <t>16 Mar 2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.441</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1.604</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5283</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.538</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1.5977</t>
+          <t>1.5516</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1.5627</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1.6115</t>
+          <t>1.5716</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>09 Feb 2026</t>
+          <t>13 Mar 2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.321</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.584</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.533</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.542</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1.5967</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1.6046</t>
+          <t>1.567</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.576</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06 Feb 2026</t>
+          <t>12 Mar 2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1.337</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.501</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.546</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.6058</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.6169</t>
+          <t>1.579</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05 Feb 2026</t>
+          <t>11 Mar 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.367</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1.614</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.5505</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1.5805</t>
+          <t>1.547</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.561</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1.6079</t>
+          <t>1.572</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>04 Feb 2026</t>
+          <t>10 Mar 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4894,1154 +4894,2094 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1.583</t>
+          <t>1.492</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5359</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1.5846</t>
+          <t>1.5492</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5614</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.5715</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.5803</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>03 Feb 2026</t>
+          <t>09 Mar 2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1.322</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.423</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1.475</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5392</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1.5859</t>
+          <t>1.5515</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1.6042</t>
+          <t>1.5636</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.5746</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1.6215</t>
+          <t>1.5825</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>02 Feb 2026</t>
+          <t>06 Mar 2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1.462</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.5417</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1.5889</t>
+          <t>1.5548</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1.6069</t>
+          <t>1.566</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.6137</t>
+          <t>1.5759</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1.6248</t>
+          <t>1.5848</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>05 Mar 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.461</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.551</t>
+          <t>1.5468</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1.589</t>
+          <t>1.558</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.579</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1.588</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>29 Jan 2026</t>
+          <t>04 Mar 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1.266</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1.415</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.454</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1.548</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1.5605</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1.5727</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.5826</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.5915</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>28 Jan 2026</t>
+          <t>03 Mar 2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1.267</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1.448</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.498</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.5546</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1.5947</t>
+          <t>1.565</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1.6099</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.6189</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.595</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>27 Jan 2026</t>
+          <t>02 Mar 2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.315</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.466</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.514</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.5556</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1.5968</t>
+          <t>1.5678</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.582</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.591</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.5994</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26 Jan 2026</t>
+          <t>28 Feb 2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.5558</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1.5978</t>
+          <t>1.5679</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1.6135</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1.6269</t>
+          <t>1.5945</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.604</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>23 Jan 2026</t>
+          <t>27 Feb 2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1.358</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.491</t>
+          <t>1.474</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>1.527</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.5577</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.586</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1.6441</t>
+          <t>1.605</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>22 Jan 2026</t>
+          <t>26 Feb 2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1.497</t>
+          <t>1.457</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.5748</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1.588</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.6327</t>
+          <t>1.5968</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>1.6068</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21 Jan 2026</t>
+          <t>25 Feb 2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1.378</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1.497</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.571</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5778</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.5979</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.608</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20 Jan 2026</t>
+          <t>24 Feb 2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1.553</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1.577</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.578</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19 Jan 2026</t>
+          <t>14 Feb 2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1.3156</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.3233</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>1.639</t>
-        </is>
-      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16 Jan 2026</t>
+          <t>13 Feb 2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.271</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1.593</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15 Jan 2026</t>
+          <t>12 Feb 2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.374</t>
+          <t>1.368</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.518</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.5596</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5951</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.599</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6089</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14 Jan 2026</t>
+          <t>11 Feb 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.366</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.523</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5511</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5958</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5997</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6092</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>13 Jan 2026</t>
+          <t>10 Feb 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1.362</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1.531</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1.604</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5977</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.602</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.6115</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>12 Jan 2026</t>
+          <t>09 Feb 2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>1.584</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5967</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6046</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6147</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>09 Jan 2026</t>
+          <t>06 Feb 2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1.277</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1.487</t>
+          <t>1.504</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.597</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6058</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>1.6169</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>08 Jan 2026</t>
+          <t>05 Feb 2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.319</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1.464</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1.614</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1.5505</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5805</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1.6079</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6189</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07 Jan 2026</t>
+          <t>04 Feb 2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1.318</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.473</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1.583</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.564</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>1.5846</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1.609</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
           <t>1.619</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>1.637</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1.649</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>06 Jan 2026</t>
+          <t>03 Feb 2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1.317</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.422</t>
+          <t>1.488</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.511</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.5859</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>1.6042</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6215</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>05 Jan 2026</t>
+          <t>02 Feb 2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1.509</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1.596</t>
+          <t>1.5889</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1.617</t>
+          <t>1.6069</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1.6137</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1.6248</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>04 Jan 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>1.328</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.598</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>1.551</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>1.589</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1.624</t>
+          <t>1.609</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.617</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>1.628</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>29 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.368</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1.572</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1.552</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1.591</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1.608</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1.629</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>28 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.366</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1.527</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.5546</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1.5947</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1.6099</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1.6189</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1.6337</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>27 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.371</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1.5556</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1.5968</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1.6094</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>26 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1.543</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1.599</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.5558</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1.5978</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1.6135</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1.6269</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>23 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.396</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1.491</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1.577</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.5577</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1.629</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1.6441</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>22 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1.413</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1.497</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1.616</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1.6327</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1.6458</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.322</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1.488</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1.483</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1.582</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1.638</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>19 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.318</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1.467</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1.501</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1.496</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1.558</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>15 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1.374</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1.5596</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>14 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1.567</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.391</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1.523</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1.534</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>12 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1.316</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1.473</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1.489</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1.556</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>09 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.272</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>1.461</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1.487</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1.557</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1.635</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1.646</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>08 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1.462</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1.482</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1.559</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1.636</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>07 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.266</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1.453</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1.564</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1.597</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1.619</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>06 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>1.422</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1.465</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1.569</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>05 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1.264</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>1.423</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1.457</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1.574</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1.596</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1.617</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1.637</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>04 Jan 2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.258</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>1.428</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1.579</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1.598</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1.624</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1.649</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Data source:</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>China Foreign Exchange Trade System (CFETS)</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
         <is>
           <t>www.chinamoney.com.cn/english/</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
